--- a/Översikt EKSJÖ.xlsx
+++ b/Översikt EKSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45013</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45204</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>45110</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>45712</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>45000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>45460</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>46135</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45764</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45285</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>45411</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>45574</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>44888</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45349</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>45122</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45349</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>45930</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44649</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>44487</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44504</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>44851</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>44544</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45328</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>44956</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>45204</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45176</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>44854</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>45898</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>45954</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>45369</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>45975</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>46163</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>46163</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>45161</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>44928</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>46106</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>44958</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45422</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>45334</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>46202</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>46283</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>45330</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>45666</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45553</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>45453</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>45195</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>45707</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>45954</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>44889</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>44781</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>44873</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44827</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>44546</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>44753</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>44620</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>44790</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>44792</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>44482</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>44525</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>44461</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>44572</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>44573</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>44496</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>44853</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>44746</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>44650</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>44873</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>44512</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44845</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44655</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>44623</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>44782</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44739</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>44477</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>44598</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>44490</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>44552</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>44477</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>44462</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>44498</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>44746</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>44861</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>44461</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>44516</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>44592</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>44616</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>44701</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>44462</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>44883</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>44467</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>44739</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>44523</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>44476</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>44748</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>44847</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>44522</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>44610</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>44480</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>44817</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>44582</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>44616</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>44879</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44630</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>44616</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>44748</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>44831</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>44980</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>45078</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>44909</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44942</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>44861</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>45003</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>44809</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>45152</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44903</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44940</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44941</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45057</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45575</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>45051</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>45264</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44949</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>45243</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>45345</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>44925</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>45344</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>45523</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>45544</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>45092</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>45281</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>45204</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>44908</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>45408</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>45715</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>45715</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>45237</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>45097</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>45355</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>44460</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>45533</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>45558</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>45530</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>45161</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>45161</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>45680</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>45076</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45485</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45231</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44888</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45716</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>45096</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45096</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>45463</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>45147</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45719</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>45601</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45532</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45686</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>45714</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45251</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>44574</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44834</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>45664</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>45418</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45485</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>44888</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45078</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>44803</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>44953</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45204</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>45245</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>45176</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>45631</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>45758</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>45358</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>45463</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>45162</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>45008</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>45216</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>45741</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>45741</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>45315</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45328</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45036</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>44580</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>45097</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>44511</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45184</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44781</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>44781</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45770</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>45837</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>45840</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45845</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>45232</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>44477</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>45232</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>45223</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>45201</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>45825</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>45086</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>45842</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>45334</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>45334</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>44991</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>45364</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>44945</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>45338</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>45758</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>45882</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>45882</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>45898</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>45628</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         <v>45757</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>45222</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>45222</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>45898</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>45195</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45391</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>45837</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>45334</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45908</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>46140</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45911</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>45251</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45911</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45911</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45911</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>45911</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45911</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45945</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45334</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45334</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44746</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44991</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45915</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>45195</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>45195</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45916</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>44928</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>45071</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>45173</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>45924</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>45161</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>45475</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>45924</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>45334</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45463</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45373</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>45337</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>44987</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>44480</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45677</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45666</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>45680</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>44630</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45286</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>45911</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>45512</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>46146</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45086</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45940</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>45944</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45946</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>45384</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45315</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45944</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45173</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45945</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45513</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>45954</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>45617</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>45706</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45954</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>45954</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22767,7 +22767,7 @@
         <v>44516</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>45576</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>44917</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>46037</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44846</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>44846</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>45365</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>46013</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23361,7 +23361,7 @@
         <v>44925</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>45239</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>45971</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45114</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45402</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45972</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45713</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45972</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45176</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45314</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45314</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>45975</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45975</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45091</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>45197</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>45659</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>45981</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45141</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>45985</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>45985</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45992</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45992</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>45232</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>45175</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>45086</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>45996</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>46162</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>46163</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>46163</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>46163</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>46163</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>46163</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>46163</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         <v>45991</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>45992</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>45238</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>46163</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>45533</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26160,7 +26160,7 @@
         <v>44783</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
         <v>45533</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         <v>45054</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>45916</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>45628</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>46009</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>44739</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>46009</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>45113</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>45523</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>45523</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26968,7 +26968,7 @@
         <v>45600</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>45533</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>46013</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>46013</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>46014</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45049</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>44853</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>45714</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>45714</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>44925</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>45212</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>45072</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>44974</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>44685</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>44846</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
         <v>44813</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>45420</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>46031</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45426</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44803</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>46034</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>46034</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>46034</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>46034</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>46034</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>45251</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>45677</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>46034</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>46034</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>45075</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>46034</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>46034</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44974</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>46037</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>46037</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>46037</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>46038</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>46174</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29772,7 +29772,7 @@
         <v>46045</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>46045</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>44846</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>44846</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>46048</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>46175</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>45468</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>46048</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>46049</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>46175</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>44713</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>45308</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>46178</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>45723</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>46056</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>45154</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45328</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>46178</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>44908</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>46069</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44615</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31310,7 +31310,7 @@
         <v>46182</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>46071</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>44909</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31539,7 +31539,7 @@
         <v>44467</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>45161</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>46183</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>46184</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>46184</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>46184</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>46184</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>45224</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>44481</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>45154</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>46188</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45706</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32415,7 +32415,7 @@
         <v>45719</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>44701</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>45161</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>45082</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32712,7 +32712,7 @@
         <v>45649</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>46098</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>46100</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32931,7 +32931,7 @@
         <v>45096</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33004,7 +33004,7 @@
         <v>46196</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>46198</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33150,7 +33150,7 @@
         <v>46106</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>46106</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>46107</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>46107</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>46107</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>45236</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>46197</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45537</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>46107</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>46107</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45278</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>46197</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34066,7 +34066,7 @@
         <v>46197</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>46079</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>46112</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>46202</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34358,7 +34358,7 @@
         <v>46113</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>46113</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>46113</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>44966</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45160</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>45370</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34811,7 +34811,7 @@
         <v>46199</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34884,7 +34884,7 @@
         <v>45068</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>44539</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35030,7 +35030,7 @@
         <v>46127</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>45253</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>46132</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>44845</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44789</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>45239</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>45370</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35541,7 +35541,7 @@
         <v>45334</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>45334</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>44865</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35775,7 +35775,7 @@
         <v>45107</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45894</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35921,7 +35921,7 @@
         <v>45204</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35994,7 +35994,7 @@
         <v>45714</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>45818</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>46029</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36223,7 +36223,7 @@
         <v>44974</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>45560</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45576</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>44490</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>46247</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>45076</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45096</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>45372</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>44623</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>45156</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>45071</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>44908</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>45391</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>44581</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>45111</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44600</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>45715</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>46209</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>46209</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>45411</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>46209</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45214</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>46252</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>45300</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>44746</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38083,7 +38083,7 @@
         <v>45300</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>46209</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38234,7 +38234,7 @@
         <v>46212</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>46255</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>46255</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>46255</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38536,7 +38536,7 @@
         <v>46255</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>45632</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>45208</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         <v>45218</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>45334</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>46255</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>46254</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39052,7 +39052,7 @@
         <v>46255</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>46212</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>44848</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>45770</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45537</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45714</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>45714</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>45715</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39656,7 +39656,7 @@
         <v>45715</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>45715</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>44851</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>45707</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>46258</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>46259</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>45329</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40177,7 +40177,7 @@
         <v>45635</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>46260</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>45334</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>45334</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>46260</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>44939</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>45561</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>46247</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>46247</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>44719</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>45762</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45671</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>44609</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>44999</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>44999</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>45209</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>45777</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>46273</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>45777</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>45779</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>45637</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>46272</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>46247</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>46274</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45706</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>45786</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45705</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>45175</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>45530</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>46281</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45790</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>45579</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45791</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45791</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>46281</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>45743</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>45624</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>45743</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>45741</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
         <v>45726</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>45741</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45741</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45728</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45741</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>45727</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>46283</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45737</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>45524</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45811</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43814,7 +43814,7 @@
         <v>45091</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43887,7 +43887,7 @@
         <v>45771</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>45819</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45819</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45826</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>45560</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44257,7 +44257,7 @@
         <v>45839</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>45841</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45841</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44481,7 +44481,7 @@
         <v>45842</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44554,7 +44554,7 @@
         <v>45845</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
         <v>45842</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45785</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44773,7 +44773,7 @@
         <v>44974</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45695</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>45461</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>45860</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45860</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45148,7 +45148,7 @@
         <v>45866</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>45874</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>45875</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45367,7 +45367,7 @@
         <v>45875</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45877</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45819</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45586,7 +45586,7 @@
         <v>45842</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45659,7 +45659,7 @@
         <v>45762</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
         <v>45349</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45805,7 +45805,7 @@
         <v>45349</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45878,7 +45878,7 @@
         <v>45349</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45951,7 +45951,7 @@
         <v>45349</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46024,7 +46024,7 @@
         <v>45100</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45100</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46170,7 +46170,7 @@
         <v>45349</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46243,7 +46243,7 @@
         <v>45103</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>45628</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45349</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46462,7 +46462,7 @@
         <v>45349</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45349</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>45042</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45349</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>45100</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45155</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45770</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45741</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45712</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45707</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>45804</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>45916</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45940</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47426,7 +47426,7 @@
         <v>46121</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>46154</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>46166</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>46190</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>46190</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>46210</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>46153</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>

--- a/Översikt EKSJÖ.xlsx
+++ b/Översikt EKSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45013</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45204</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>45110</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45712</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>45000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45460</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>46135</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>45411</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>44888</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45764</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>45285</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>45574</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>45349</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45122</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>45349</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>45930</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44649</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44487</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>44504</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>44851</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44544</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>45334</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>44854</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45369</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45328</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>45330</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>45898</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>44928</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>46106</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>45954</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>45975</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>45666</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>46163</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>46163</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>45422</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>46202</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>44956</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>45176</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>45161</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>46283</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>45204</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>44958</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>45553</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>45453</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45195</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>45707</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>45954</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44889</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>44781</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44873</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44827</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44546</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44753</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>44620</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>44790</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>44792</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>44482</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>44525</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>44572</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>44496</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>44573</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>44853</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>44650</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>44746</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>44873</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>44512</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>44845</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>44655</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>44623</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>44782</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>44739</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>44477</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>44598</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>44490</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>44552</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>44477</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44498</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>44861</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44746</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>44592</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>44616</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>44701</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44883</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>44739</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>44467</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44523</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>44476</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>44748</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44847</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>44522</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>44610</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>44480</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>44817</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>44582</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>44616</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>44630</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44879</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>44748</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>44616</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>44831</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>44991</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>45334</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>45334</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>45334</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>45334</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>44834</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45232</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>45512</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>45334</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45719</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>45355</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>45076</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>45716</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>45184</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>45049</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>44809</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45245</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>44481</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>45096</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>45300</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>45370</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>44846</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44846</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>44903</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>45533</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>44974</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>45533</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>44865</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>45154</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>44942</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>45741</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>45728</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>45113</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45727</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>45743</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45741</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>45743</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45334</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45334</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>46034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>45741</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>45741</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>46034</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>46034</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>46034</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>46034</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>46034</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>46034</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>46034</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>45837</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>46031</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>44477</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>45726</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45845</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>45840</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>45530</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>46037</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>44861</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>45825</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45485</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>46038</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>46037</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>46037</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45624</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45898</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45898</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>45195</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>46045</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>46045</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>46048</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>46048</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>45533</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45837</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>46049</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>44600</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>45908</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44909</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>45544</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44490</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>46056</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45537</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>45911</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>45911</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>45911</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>45558</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>45911</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>45911</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>45911</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45216</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45916</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>45218</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>45915</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>44574</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>45737</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>45924</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>45513</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>46069</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>45924</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>46071</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>44888</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45408</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>45524</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>45091</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45372</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45911</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>44974</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>44623</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45940</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45384</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45576</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45533</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45771</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>44928</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45944</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>46098</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>45364</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>45946</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>46100</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45944</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>44701</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45251</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>44713</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45463</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>46107</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>46107</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>46107</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>46107</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>46107</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>45945</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>46106</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>46106</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>45954</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45954</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45076</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>45954</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45811</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>46112</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>44803</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>46113</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>46113</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>46113</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>45715</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44909</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45628</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45086</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>46127</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>45972</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45972</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>45971</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45003</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45632</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>45975</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>46132</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>44719</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>45036</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45975</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>45365</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45096</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45096</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>45981</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45114</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>45628</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45985</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>45985</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45842</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>45882</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
         <v>45758</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45631</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45992</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45992</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45992</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>45991</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>45894</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44783</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>44853</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>45945</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>45156</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>45251</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45715</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>45485</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>45161</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>45161</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>45818</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45237</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45706</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>44813</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45819</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45224</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45819</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45715</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>45715</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24174,7 +24174,7 @@
         <v>45719</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24247,7 +24247,7 @@
         <v>46009</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>46009</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>46013</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>46014</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>46013</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45714</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45714</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>44945</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>45008</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>45882</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>45671</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45334</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25153,7 +25153,7 @@
         <v>45826</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>45197</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>45173</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>45238</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>45072</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>45418</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25591,7 +25591,7 @@
         <v>45068</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>45741</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>45071</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>44991</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45111</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>46146</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>44908</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>45741</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>44480</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>45757</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>45222</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>45560</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26487,7 +26487,7 @@
         <v>46013</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>46037</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>45996</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>45097</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>45092</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26852,7 +26852,7 @@
         <v>45839</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>45841</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45841</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>45842</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>46162</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>44966</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>45845</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>46163</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>46163</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>46163</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>45842</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>46163</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>46163</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>44953</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>46163</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>45391</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>46163</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>44974</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45147</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>45695</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45785</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>45916</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>45561</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45461</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>45860</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44917</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45860</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>45537</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>46175</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>46174</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>45334</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44980</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>46175</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>45866</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>45560</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>44511</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>46178</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>45468</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>45315</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>46178</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>45664</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>46182</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29948,7 +29948,7 @@
         <v>46183</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>44609</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>46184</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>45251</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>46184</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30313,7 +30313,7 @@
         <v>45161</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>46184</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>45344</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>46184</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>46188</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>45874</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30751,7 +30751,7 @@
         <v>45402</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>45635</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>45071</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30970,7 +30970,7 @@
         <v>45523</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>45875</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>45875</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>44999</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>44999</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>45329</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>45204</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>45877</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>45819</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>46197</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>46197</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>45842</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>45706</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45714</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>45714</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45714</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45714</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>46197</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45345</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>46199</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>46079</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>44581</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>46202</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>44615</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45762</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>45232</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>45173</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>45078</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>45204</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>46209</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33195,7 +33195,7 @@
         <v>45686</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>45677</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>46252</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>45176</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>45239</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>46212</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45231</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>46209</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>46209</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>46212</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>46254</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45162</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>46209</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>46255</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>46255</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>45232</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>45161</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34451,7 +34451,7 @@
         <v>45420</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>46255</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>46255</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>46255</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>46255</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>46258</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>45223</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>45666</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45523</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35118,7 +35118,7 @@
         <v>45523</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35191,7 +35191,7 @@
         <v>45770</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45195</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>45195</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>46259</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35488,7 +35488,7 @@
         <v>45175</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35561,7 +35561,7 @@
         <v>45680</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44685</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>45236</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>45707</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>44908</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45239</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45315</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45314</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>45314</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>45463</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>45328</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45328</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>45758</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>45715</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36603,7 +36603,7 @@
         <v>44746</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>46272</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45176</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>44888</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>45264</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>44908</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>46273</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>44846</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>44846</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37265,7 +37265,7 @@
         <v>45358</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>46274</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>45243</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>44630</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>45209</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>44851</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>45160</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>46281</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45097</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44848</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>45532</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>44987</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>46034</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>46281</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>45391</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>46283</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>46196</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>45576</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>44739</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>44539</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>46247</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>46247</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>44939</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38959,7 +38959,7 @@
         <v>46247</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>45086</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>45091</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>46247</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>45051</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>46289</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>44789</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>46260</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>46289</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45411</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>45082</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>46289</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39850,7 +39850,7 @@
         <v>45086</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39923,7 +39923,7 @@
         <v>44925</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>45078</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45154</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>44516</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>45278</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40288,7 +40288,7 @@
         <v>44746</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>44781</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40434,7 +40434,7 @@
         <v>44781</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>45337</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>45680</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>45201</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>44974</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45281</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>44949</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45713</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>45057</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45253</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45286</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45659</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>45762</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>45370</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>45075</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>45096</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>45152</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>44467</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>44925</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>44940</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>44941</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>45214</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45204</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45212</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45649</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45141</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>45054</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>44846</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>44845</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45300</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>44803</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>45208</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45107</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>44925</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>45373</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>45601</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45308</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>45334</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>45463</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43301,7 +43301,7 @@
         <v>45161</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45617</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         <v>44580</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45475</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45715</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>45677</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45723</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45222</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45338</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43963,7 +43963,7 @@
         <v>45575</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>45600</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44114,7 +44114,7 @@
         <v>45770</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45426</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45777</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45777</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>45779</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>45637</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>45175</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45706</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45786</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45790</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45705</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45530</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>45791</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>45791</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45156,7 +45156,7 @@
         <v>45579</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45229,7 +45229,7 @@
         <v>45349</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45302,7 +45302,7 @@
         <v>45349</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45349</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45349</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45100</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45594,7 +45594,7 @@
         <v>45100</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45349</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>45103</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45628</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>45349</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45959,7 +45959,7 @@
         <v>45349</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46032,7 +46032,7 @@
         <v>45349</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46105,7 +46105,7 @@
         <v>45042</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45349</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45100</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45155</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>45770</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46475,7 +46475,7 @@
         <v>45741</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>45712</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45707</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45804</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>45916</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45940</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46923,7 +46923,7 @@
         <v>46121</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>46154</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>46166</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>46190</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>46190</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>46153</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>46210</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>

--- a/Översikt EKSJÖ.xlsx
+++ b/Översikt EKSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45013</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45204</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>45110</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45712</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>45000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45460</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>46135</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>45411</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>44888</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45764</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>45285</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>45574</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>45349</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45122</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>45349</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>45930</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44649</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44487</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>44504</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>44851</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44544</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>45334</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>44854</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45369</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45328</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>45330</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>45898</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>44928</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>46106</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>45954</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>45975</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>45666</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>46163</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>46163</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>45422</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>46202</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>44956</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>45176</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>45161</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>46283</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>45204</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>44958</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>45553</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>45453</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45195</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>45707</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>45954</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44889</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>44781</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44873</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44827</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44546</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44753</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>44620</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>44790</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>44792</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>44482</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>44525</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>44572</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>44496</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>44573</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>44853</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>44650</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>44746</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>44873</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>44512</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>44845</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>44655</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>44623</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>44782</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>44739</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>44477</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>44598</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>44490</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>44552</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>44477</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44498</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>44861</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44746</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>44592</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>44616</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>44701</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44883</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>44739</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>44467</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44523</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>44476</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>44748</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44847</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>44522</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>44610</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>44480</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>44817</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>44582</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>44616</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>44630</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44879</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>44748</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>44616</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>44831</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>44991</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>45334</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>45334</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>45334</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>45334</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>44834</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45232</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>45512</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>45334</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45719</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>45355</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>45076</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>45716</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>45184</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>45049</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>44809</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45245</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>44481</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>45096</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>45300</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>45370</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>44846</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44846</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>44903</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>45533</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>44974</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>45533</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>44865</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>45154</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>44942</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>45741</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>45728</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>45113</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45727</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>45743</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45741</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>45743</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45334</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45334</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>46034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>45741</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>45741</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>46034</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>46034</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>46034</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>46034</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>46034</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>46034</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>46034</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>45837</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>46031</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>44477</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>45726</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45845</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>45840</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>45530</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>46037</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>44861</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>45825</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45485</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>46038</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>46037</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>46037</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45624</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45898</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45898</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>45195</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>46045</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>46045</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>46048</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>46048</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>45533</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45837</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>46049</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>44600</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>45908</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44909</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>45544</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44490</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>46056</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45537</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>45911</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>45911</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>45911</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>45558</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>45911</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>45911</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>45911</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45216</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45916</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>45218</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>45915</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>44574</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>45737</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>45924</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>45513</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>46069</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>45924</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>46071</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>44888</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45408</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>45524</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>45091</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45372</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45911</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>44974</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>44623</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45940</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45384</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45576</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45533</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45771</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>44928</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45944</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>46098</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>45364</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>45946</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>46100</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45944</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>44701</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45251</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>44713</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45463</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>46107</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>46107</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>46107</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>46107</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>46107</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>45945</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>46106</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>46106</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>45954</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45954</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45076</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>45954</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45811</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>46112</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>44803</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>46113</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>46113</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>46113</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>45715</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44909</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45628</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45086</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>46127</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>45972</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45972</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>45971</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45003</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45632</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>45975</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>46132</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>44719</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>45036</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45975</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>45365</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45096</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45096</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>45981</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45114</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>45628</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45985</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>45985</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45842</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>45882</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
         <v>45758</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45631</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45992</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45992</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45992</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>45991</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>45894</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44783</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>44853</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>45945</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>45156</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>45251</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45715</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>45485</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>45161</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>45161</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>45818</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45237</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45706</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>44813</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45819</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45224</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45819</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45715</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>45715</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24174,7 +24174,7 @@
         <v>45719</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24247,7 +24247,7 @@
         <v>46009</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>46009</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>46013</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>46014</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>46013</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45714</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45714</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>44945</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>45008</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>45882</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>45671</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45334</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25153,7 +25153,7 @@
         <v>45826</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>45197</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>45173</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>45238</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>45072</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>45418</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25591,7 +25591,7 @@
         <v>45068</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>45741</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>45071</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>44991</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45111</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>46146</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>44908</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>45741</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>44480</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>45757</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>45222</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>45560</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26487,7 +26487,7 @@
         <v>46013</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>46037</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>45996</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>45097</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>45092</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26852,7 +26852,7 @@
         <v>45839</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>45841</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45841</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>45842</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>46162</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>44966</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>45845</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>46163</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>46163</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>46163</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>45842</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>46163</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>46163</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>44953</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>46163</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>45391</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>46163</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>44974</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45147</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>45695</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45785</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>45916</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>45561</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45461</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>45860</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44917</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45860</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>45537</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>46175</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>46174</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>45334</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44980</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>46175</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>45866</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>45560</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>44511</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>46178</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>45468</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>45315</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>46178</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>45664</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>46182</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29948,7 +29948,7 @@
         <v>46183</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>44609</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>46184</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>45251</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>46184</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30313,7 +30313,7 @@
         <v>45161</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>46184</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>45344</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>46184</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>46188</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>45874</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30751,7 +30751,7 @@
         <v>45402</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>45635</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>45071</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30970,7 +30970,7 @@
         <v>45523</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>45875</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>45875</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>44999</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>44999</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>45329</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>45204</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>45877</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>45819</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>46197</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>46197</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>45842</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>45706</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45714</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>45714</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45714</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45714</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>46197</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45345</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>46199</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>46079</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>44581</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>46202</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>44615</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45762</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>45232</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>45173</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>45078</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>45204</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>46209</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33195,7 +33195,7 @@
         <v>45686</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>45677</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>46252</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>45176</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>45239</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>46212</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45231</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>46209</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>46209</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>46212</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>46254</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45162</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>46209</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>46255</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>46255</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>45232</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>45161</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34451,7 +34451,7 @@
         <v>45420</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>46255</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>46255</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>46255</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>46255</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>46258</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>45223</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>45666</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45523</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35118,7 +35118,7 @@
         <v>45523</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35191,7 +35191,7 @@
         <v>45770</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45195</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>45195</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>46259</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35488,7 +35488,7 @@
         <v>45175</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35561,7 +35561,7 @@
         <v>45680</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44685</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>45236</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>45707</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>44908</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45239</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45315</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45314</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>45314</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>45463</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>45328</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45328</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>45758</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>45715</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36603,7 +36603,7 @@
         <v>44746</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>46272</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45176</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>44888</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>45264</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>44908</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>46273</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>44846</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>44846</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37265,7 +37265,7 @@
         <v>45358</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>46274</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>45243</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>44630</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>45209</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>44851</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>45160</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>46281</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45097</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44848</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>45532</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>44987</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>46034</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>46281</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>45391</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>46283</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>46196</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>45576</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>44739</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>44539</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>46247</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>46247</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>44939</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38959,7 +38959,7 @@
         <v>46247</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>45086</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>45091</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>46247</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>45051</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>46289</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>44789</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>46260</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>46289</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45411</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>45082</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>46289</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39850,7 +39850,7 @@
         <v>45086</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39923,7 +39923,7 @@
         <v>44925</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>45078</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45154</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>44516</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>45278</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40288,7 +40288,7 @@
         <v>44746</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>44781</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40434,7 +40434,7 @@
         <v>44781</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>45337</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>45680</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>45201</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>44974</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45281</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>44949</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45713</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>45057</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45253</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45286</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45659</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>45762</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>45370</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>45075</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>45096</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>45152</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>44467</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>44925</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>44940</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>44941</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>45214</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45204</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45212</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45649</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45141</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>45054</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>44846</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>44845</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45300</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>44803</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>45208</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45107</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>44925</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>45373</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>45601</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45308</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>45334</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>45463</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43301,7 +43301,7 @@
         <v>45161</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45617</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         <v>44580</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45475</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45715</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>45677</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45723</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45222</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45338</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43963,7 +43963,7 @@
         <v>45575</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>45600</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44114,7 +44114,7 @@
         <v>45770</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45426</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45777</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45777</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>45779</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>45637</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>45175</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45706</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45786</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45790</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45705</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45530</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>45791</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>45791</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45156,7 +45156,7 @@
         <v>45579</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45229,7 +45229,7 @@
         <v>45349</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45302,7 +45302,7 @@
         <v>45349</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45349</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45349</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45100</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45594,7 +45594,7 @@
         <v>45100</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45349</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>45103</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45628</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>45349</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45959,7 +45959,7 @@
         <v>45349</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46032,7 +46032,7 @@
         <v>45349</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46105,7 +46105,7 @@
         <v>45042</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45349</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45100</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45155</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>45770</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46475,7 +46475,7 @@
         <v>45741</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>45712</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45707</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45804</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>45916</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45940</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46923,7 +46923,7 @@
         <v>46121</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>46154</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>46166</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>46190</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>46190</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>46153</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>46210</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>

--- a/Översikt EKSJÖ.xlsx
+++ b/Översikt EKSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45013</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45204</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45110</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>45712</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45460</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46135</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45764</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45285</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45411</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>45574</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>44888</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>46297</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>45349</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45122</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45349</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44649</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>44504</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>44544</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45328</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45898</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>44956</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>45330</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>45204</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>45954</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>45176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>45975</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>46106</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>44854</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>45666</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>45369</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>46163</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>46163</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45161</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>44928</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>46283</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>46297</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44958</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>45422</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45334</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>45553</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>45453</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>45195</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>45707</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>45954</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>44889</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>44781</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>44873</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>44827</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>44546</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>44753</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44620</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44790</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>44792</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>44482</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>44525</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44572</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>44573</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>44496</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>44853</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>44746</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44650</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>44873</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>44512</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44845</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44655</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44623</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44782</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>44739</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>44477</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>44598</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>44490</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>44552</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>44477</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>44498</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>44861</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>44746</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>44516</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44592</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>44616</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44701</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>44883</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>44739</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>44523</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>44476</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44748</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44847</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44522</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44610</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44480</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>44817</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44582</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>44616</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>44630</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         <v>44748</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44879</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>44616</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44831</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44980</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>45078</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>44942</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45575</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>45003</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>44909</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>44861</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>45152</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>44903</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>44809</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>45051</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>45264</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>44940</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>44941</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>44949</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45057</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>44925</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>45344</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>45243</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>45544</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45092</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>45281</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>45345</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>45523</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>45786</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>45705</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>45175</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>45204</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>44908</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45408</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>45097</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>45530</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>45715</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45715</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>45790</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>45237</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>45355</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>46009</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>45533</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>46009</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>46013</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>46013</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>46014</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45837</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45840</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45845</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45530</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45558</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>45825</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45161</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>45161</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>45680</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>46031</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45579</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>45485</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45898</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>46034</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45898</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>46034</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>46034</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>46034</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>45791</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>46034</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>46034</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>45076</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>46034</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>45195</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>45837</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>46037</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>46037</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>46037</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>44888</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>46038</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>45231</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>45908</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>45791</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>45911</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>45911</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>45911</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>45911</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>45911</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45911</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>46045</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>46045</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45915</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>46048</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45743</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45624</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45916</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45743</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45741</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>45726</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45463</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45716</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>46048</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45096</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>45096</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45741</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>45741</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>45728</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>46049</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>45741</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>45727</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>45737</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>45524</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>45924</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>45601</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>45532</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>45924</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>45147</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>46056</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>45719</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>45686</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>45811</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>44574</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>46069</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>45714</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>45251</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>44834</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>45664</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>45911</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>46071</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45485</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45418</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45940</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>44888</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45944</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45091</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45946</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45771</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>45944</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45078</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45945</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>44953</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45954</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45204</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45954</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>45954</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>44803</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>45631</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>45358</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45176</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>45463</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45245</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45758</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>45162</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>45971</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>46098</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45972</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>46100</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45972</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>44580</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>45097</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45975</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45975</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45216</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>46106</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>46106</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>45008</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>45819</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>46107</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>46107</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>46107</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>46107</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45741</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>45741</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45981</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>46107</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45819</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>45985</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>45315</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45036</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>45985</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>46112</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>46113</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>46113</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>46113</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>45328</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>44511</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>45992</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23360,7 +23360,7 @@
         <v>45992</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>45184</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45991</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         <v>45992</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>44781</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>44781</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>46127</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         <v>45826</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>45770</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>46132</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>45232</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45223</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45201</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>45086</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>45560</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45894</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>45334</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>44991</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>45364</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>44945</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45839</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>45818</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45338</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45757</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45222</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45222</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45841</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45841</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45391</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45842</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45845</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45334</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>45842</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45785</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45334</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45334</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44974</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44746</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45195</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45195</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>45695</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>44928</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45071</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>45173</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45842</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>45461</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26773,7 +26773,7 @@
         <v>45161</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>45758</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>45882</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>45882</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>45475</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>45628</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>45334</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>45463</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27367,7 +27367,7 @@
         <v>45373</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>45860</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>45337</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27586,7 +27586,7 @@
         <v>45860</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>44987</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>44480</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>45677</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>45666</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>45680</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>45251</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>45866</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>45945</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44630</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>45286</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28394,7 +28394,7 @@
         <v>45512</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>44991</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>45086</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>45384</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28686,7 +28686,7 @@
         <v>45315</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>45173</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28832,7 +28832,7 @@
         <v>45513</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>46146</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45617</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>45706</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>44516</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         <v>45576</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>44917</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>46037</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>46013</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>44846</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44846</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45365</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>44925</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>45239</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>45114</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>45402</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45874</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>45713</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45176</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45314</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45314</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45996</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45875</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45875</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>46162</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>46163</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>46163</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>46163</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>46163</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45819</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>46163</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>46163</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>46163</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45091</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45197</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>45916</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45659</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45141</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45842</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>46174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45762</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>46175</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>45232</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>45175</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>46175</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>46178</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45232</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45086</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>44477</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>46178</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>46182</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>45238</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>46183</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>46184</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>46184</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>46184</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>46184</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45533</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>44783</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>46188</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>45533</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>45054</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>45628</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>44739</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>45113</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45523</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45523</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>45600</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>45533</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>45049</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>46197</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44853</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>46197</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>45714</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45714</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>46197</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44925</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>46079</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>45212</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>46202</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45072</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>44974</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>46199</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>44685</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>44846</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>44813</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45420</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45426</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>44803</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45251</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>45677</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45075</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>44974</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>46209</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>46209</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>46209</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>46209</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>46212</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>46212</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>45770</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>44846</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>44846</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>46258</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>46259</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>45468</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>44713</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>45308</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45723</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45154</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45328</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>44908</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>44615</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>44909</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>46273</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37239,7 +37239,7 @@
         <v>45161</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37312,7 +37312,7 @@
         <v>46272</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>46274</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>45224</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>44481</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>45154</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>46281</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>45706</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>45719</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>44701</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>45161</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45082</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38120,7 +38120,7 @@
         <v>45649</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>46281</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>46283</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45096</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>46196</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>45236</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>45537</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>45278</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>46034</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>46289</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>44966</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>45160</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45370</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>46289</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>46247</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45068</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>44539</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>46260</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>46247</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39527,7 +39527,7 @@
         <v>46247</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45253</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39678,7 +39678,7 @@
         <v>44845</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44789</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>45239</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>45370</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>45334</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>45334</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>44865</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45107</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45204</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45714</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>46252</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40501,7 +40501,7 @@
         <v>44974</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45560</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45576</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>46297</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40803,7 +40803,7 @@
         <v>46255</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>44490</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>46255</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>46247</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>46297</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45076</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>46289</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45096</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>46255</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>46255</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>46254</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>45372</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>44623</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>45156</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41845,7 +41845,7 @@
         <v>45071</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>46294</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>44908</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42064,7 +42064,7 @@
         <v>46255</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
         <v>46297</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42210,7 +42210,7 @@
         <v>46255</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45877</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>45391</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>44581</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45111</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44600</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>45715</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42726,7 +42726,7 @@
         <v>45411</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>45214</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42872,7 +42872,7 @@
         <v>45300</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>44746</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45300</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>45632</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45208</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>45218</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>45334</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>44848</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43461,7 +43461,7 @@
         <v>45537</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43534,7 +43534,7 @@
         <v>45714</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>45714</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43690,7 +43690,7 @@
         <v>45715</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43768,7 +43768,7 @@
         <v>45715</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>45715</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>44851</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         <v>45707</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45329</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44143,7 +44143,7 @@
         <v>45635</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>45334</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45334</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44939</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45561</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>44719</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44596,7 +44596,7 @@
         <v>45762</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>45671</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>44609</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44815,7 +44815,7 @@
         <v>44999</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>44999</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45209</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>45777</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>45777</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>45779</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45637</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>45706</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>45349</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>45349</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>45349</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>45349</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45706,7 +45706,7 @@
         <v>45100</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45100</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45349</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>45103</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45628</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46071,7 +46071,7 @@
         <v>45349</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46144,7 +46144,7 @@
         <v>45349</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45349</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46290,7 +46290,7 @@
         <v>45042</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>45349</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>45100</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>45155</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45770</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46660,7 +46660,7 @@
         <v>45741</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46738,7 +46738,7 @@
         <v>45712</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>45707</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>45804</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45916</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45940</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>46121</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>46154</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>46166</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>46190</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>46190</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>46210</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>46153</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>

--- a/Översikt EKSJÖ.xlsx
+++ b/Översikt EKSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45013</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45204</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45110</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>45712</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45460</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46135</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45764</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45285</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45411</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>45574</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>44888</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>46297</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>45349</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45122</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45349</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44649</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>44504</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>44544</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45328</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45898</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>44956</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>45330</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>45204</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>45954</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>45176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>45975</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>46106</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>44854</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>45666</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>45369</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>46163</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>46163</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45161</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>44928</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>46283</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>46297</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44958</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>45422</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45334</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>45553</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>45453</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>45195</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>45707</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>45954</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>44889</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>44781</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>44873</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>44827</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>44546</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>44753</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44620</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44790</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>44792</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>44482</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>44525</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44572</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>44573</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>44496</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>44853</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>44746</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44650</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>44873</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>44512</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44845</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44655</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44623</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44782</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>44739</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>44477</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>44598</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>44490</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>44552</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>44477</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>44498</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>44861</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>44746</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>44516</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44592</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>44616</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44701</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>44883</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>44739</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>44523</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>44476</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44748</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44847</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44522</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44610</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44480</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>44817</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44582</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>44616</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>44630</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         <v>44748</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44879</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>44616</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44831</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44980</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>45078</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>44942</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45575</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>45003</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>44909</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>44861</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>45152</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>44903</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>44809</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>45051</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>45264</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>44940</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>44941</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>44949</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45057</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>44925</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>45344</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>45243</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>45544</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45092</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>45281</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>45345</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>45523</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>45786</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>45705</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>45175</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>45204</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>44908</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45408</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>45097</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>45530</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>45715</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45715</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>45790</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>45237</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>45355</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>46009</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>45533</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>46009</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>46013</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>46013</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>46014</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45837</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45840</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45845</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45530</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45558</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>45825</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45161</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>45161</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>45680</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>46031</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45579</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>45485</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45898</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>46034</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45898</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>46034</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>46034</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>46034</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>45791</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>46034</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>46034</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>45076</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>46034</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>45195</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>45837</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>46037</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>46037</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>46037</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>44888</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>46038</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>45231</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>45908</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>45791</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>45911</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>45911</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>45911</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>45911</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>45911</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45911</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>46045</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>46045</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45915</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>46048</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45743</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45624</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45916</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45743</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45741</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>45726</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45463</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45716</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>46048</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45096</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>45096</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45741</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>45741</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>45728</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>46049</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>45741</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>45727</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>45737</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>45524</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>45924</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>45601</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>45532</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>45924</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>45147</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>46056</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>45719</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>45686</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>45811</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>44574</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>46069</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>45714</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>45251</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>44834</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>45664</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>45911</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>46071</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45485</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45418</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45940</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>44888</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45944</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45091</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45946</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45771</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>45944</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45078</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45945</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>44953</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45954</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45204</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45954</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>45954</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>44803</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>45631</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>45358</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45176</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>45463</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45245</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45758</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>45162</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>45971</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>46098</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45972</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>46100</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45972</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>44580</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>45097</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45975</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45975</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45216</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>46106</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>46106</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>45008</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>45819</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>46107</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>46107</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>46107</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>46107</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45741</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>45741</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45981</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>46107</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45819</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>45985</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>45315</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45036</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>45985</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>46112</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>46113</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>46113</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>46113</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>45328</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>44511</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>45992</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23360,7 +23360,7 @@
         <v>45992</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>45184</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45991</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         <v>45992</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>44781</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>44781</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>46127</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         <v>45826</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>45770</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>46132</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>45232</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45223</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45201</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>45086</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>45560</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45894</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>45334</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>44991</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>45364</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>44945</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45839</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>45818</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45338</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45757</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45222</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45222</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45841</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45841</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45391</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45842</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45845</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45334</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>45842</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45785</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45334</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45334</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44974</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44746</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45195</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45195</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>45695</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>44928</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45071</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>45173</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45842</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>45461</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26773,7 +26773,7 @@
         <v>45161</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>45758</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>45882</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>45882</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>45475</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>45628</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>45334</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>45463</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27367,7 +27367,7 @@
         <v>45373</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>45860</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>45337</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27586,7 +27586,7 @@
         <v>45860</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>44987</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>44480</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>45677</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>45666</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>45680</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>45251</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>45866</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>45945</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44630</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>45286</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28394,7 +28394,7 @@
         <v>45512</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>44991</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>45086</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>45384</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28686,7 +28686,7 @@
         <v>45315</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>45173</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28832,7 +28832,7 @@
         <v>45513</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>46146</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45617</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>45706</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>44516</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         <v>45576</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>44917</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>46037</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>46013</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>44846</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44846</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45365</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>44925</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>45239</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>45114</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>45402</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45874</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>45713</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45176</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45314</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45314</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45996</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45875</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45875</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>46162</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>46163</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>46163</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>46163</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>46163</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45819</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>46163</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>46163</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>46163</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45091</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45197</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>45916</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45659</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45141</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45842</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>46174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45762</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>46175</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>45232</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>45175</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>46175</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>46178</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45232</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45086</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>44477</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>46178</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>46182</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>45238</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>46183</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>46184</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>46184</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>46184</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>46184</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45533</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>44783</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>46188</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>45533</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>45054</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>45628</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>44739</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>45113</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45523</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45523</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>45600</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>45533</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>45049</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>46197</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44853</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>46197</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>45714</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45714</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>46197</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44925</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>46079</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>45212</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>46202</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45072</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>44974</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>46199</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>44685</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>44846</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>44813</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45420</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45426</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>44803</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45251</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>45677</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45075</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>44974</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>46209</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>46209</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>46209</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>46209</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>46212</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>46212</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>45770</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>44846</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>44846</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>46258</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>46259</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>45468</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>44713</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>45308</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45723</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45154</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45328</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>44908</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>44615</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>44909</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>46273</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37239,7 +37239,7 @@
         <v>45161</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37312,7 +37312,7 @@
         <v>46272</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>46274</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>45224</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>44481</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>45154</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>46281</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>45706</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>45719</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>44701</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>45161</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45082</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38120,7 +38120,7 @@
         <v>45649</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>46281</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>46283</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45096</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>46196</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>45236</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>45537</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>45278</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>46034</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>46289</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>44966</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>45160</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45370</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>46289</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>46247</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45068</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>44539</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>46260</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>46247</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39527,7 +39527,7 @@
         <v>46247</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45253</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39678,7 +39678,7 @@
         <v>44845</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44789</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>45239</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>45370</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>45334</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>45334</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>44865</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45107</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45204</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45714</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>46252</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40501,7 +40501,7 @@
         <v>44974</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45560</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45576</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>46297</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40803,7 +40803,7 @@
         <v>46255</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>44490</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>46255</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>46247</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>46297</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45076</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>46289</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45096</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>46255</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>46255</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>46254</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>45372</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>44623</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>45156</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41845,7 +41845,7 @@
         <v>45071</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>46294</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>44908</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42064,7 +42064,7 @@
         <v>46255</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
         <v>46297</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42210,7 +42210,7 @@
         <v>46255</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45877</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>45391</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>44581</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45111</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44600</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>45715</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42726,7 +42726,7 @@
         <v>45411</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>45214</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42872,7 +42872,7 @@
         <v>45300</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>44746</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45300</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>45632</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45208</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>45218</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>45334</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>44848</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43461,7 +43461,7 @@
         <v>45537</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43534,7 +43534,7 @@
         <v>45714</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>45714</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43690,7 +43690,7 @@
         <v>45715</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43768,7 +43768,7 @@
         <v>45715</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>45715</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>44851</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         <v>45707</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45329</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44143,7 +44143,7 @@
         <v>45635</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>45334</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45334</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44939</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45561</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>44719</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44596,7 +44596,7 @@
         <v>45762</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>45671</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>44609</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44815,7 +44815,7 @@
         <v>44999</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>44999</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45209</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>45777</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>45777</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>45779</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45637</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>45706</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>45349</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>45349</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>45349</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>45349</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45706,7 +45706,7 @@
         <v>45100</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45100</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45349</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>45103</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45628</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46071,7 +46071,7 @@
         <v>45349</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46144,7 +46144,7 @@
         <v>45349</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45349</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46290,7 +46290,7 @@
         <v>45042</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>45349</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>45100</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>45155</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45770</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46660,7 +46660,7 @@
         <v>45741</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46738,7 +46738,7 @@
         <v>45712</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>45707</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>45804</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45916</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45940</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>46121</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>46154</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>46166</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>46190</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>46190</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>46210</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>46153</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>

--- a/Översikt EKSJÖ.xlsx
+++ b/Översikt EKSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45013</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45204</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45110</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>45712</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45460</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46135</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45411</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>45285</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>45574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45764</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>44888</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>46297</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>45349</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45122</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45349</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44649</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>44851</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>44504</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>44544</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45369</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45334</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>44854</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>45328</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>45898</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45422</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45330</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>44928</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>45954</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>45666</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44956</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>45975</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>45176</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>45161</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>46106</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45204</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>44958</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>46163</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>46163</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>46283</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>46297</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>46302</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>45553</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>45453</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>45195</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>45707</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>45954</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>44889</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>44781</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44873</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44827</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>44546</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44753</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>44620</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>44790</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44792</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>44482</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>44525</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>44572</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>44573</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>44496</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>44853</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>44746</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>44650</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44873</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44512</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>44845</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>44655</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>44623</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>44782</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>44739</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>44598</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>44552</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>44490</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>44616</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44522</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44610</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44701</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>44748</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44480</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>44861</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>44498</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44746</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>44516</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44739</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44883</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>44847</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44817</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44592</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44523</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44582</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>44616</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>45355</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>44748</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>44630</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>44879</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>45659</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>45762</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>44809</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44480</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>44616</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44831</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>45757</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45370</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>45222</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44991</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>45075</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>45096</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>45152</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>44925</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45716</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>45184</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>45096</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>45049</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>45245</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>44940</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44941</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45334</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45334</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>45214</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>45204</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>44834</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>45097</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>44481</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>45300</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>45212</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>45092</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>45512</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>45649</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>45334</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>45370</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>45141</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>44846</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>44846</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>44966</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>45054</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>45719</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>45076</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>44953</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>45391</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>44846</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>45232</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44845</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45300</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>44803</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>45147</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45208</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>45107</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>44925</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>45561</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>45232</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>45533</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>44974</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>45373</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>44903</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>45533</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>45601</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44865</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45308</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45837</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>45154</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>45463</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45161</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>44917</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>45617</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>45845</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>44942</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>45840</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45537</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45113</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>44580</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>45334</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>45334</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45334</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45825</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45475</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45898</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>44980</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45715</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45677</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>45898</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45723</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45222</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>45195</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45338</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45530</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45575</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45837</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>44861</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45485</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45560</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>44511</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45600</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>45770</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45908</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45426</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45468</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45911</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45533</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>45911</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>45911</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45777</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45777</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45315</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>44600</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45911</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45911</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45664</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>45779</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>45637</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>45916</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>44909</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>45544</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>44609</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>44490</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>45537</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>45251</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>45558</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18834,7 +18834,7 @@
         <v>45161</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>45175</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>45344</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>45216</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>45706</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>45786</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45218</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>44574</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>45402</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>45635</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>45924</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>45790</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45705</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>45071</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>45530</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45513</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45924</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45523</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>44999</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44999</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>45329</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>45204</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>45791</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>45791</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44888</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>45408</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>45579</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45706</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>45714</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20966,7 +20966,7 @@
         <v>45714</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>45714</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>45714</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45345</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45741</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>45728</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>45727</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45743</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45741</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>45743</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>44581</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>45372</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21872,7 +21872,7 @@
         <v>45741</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45741</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>45726</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>44615</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>44974</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44623</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45624</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45384</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45576</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>45173</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>45533</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45078</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45737</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>44928</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45204</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45364</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45911</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45524</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45686</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>44701</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45677</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45091</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45251</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>44713</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>45463</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>45771</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45940</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45176</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45239</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>45811</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45231</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45944</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>45946</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45076</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45162</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>44803</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>45944</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>45715</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44909</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45232</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45161</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45819</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45628</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>45420</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45819</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45086</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>45826</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45223</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45666</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45523</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45523</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45195</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>45195</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>45945</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45954</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>45954</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>45954</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>45003</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26171,7 +26171,7 @@
         <v>45175</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>45632</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>45680</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>45560</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44719</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>45036</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>44685</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>45236</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>45707</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>45365</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>45096</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>45096</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44908</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45839</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45841</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>45841</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45114</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45842</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45972</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>45845</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>45972</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45971</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45842</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>45239</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>45631</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45315</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>44974</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>45695</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45975</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45785</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45314</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45314</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45463</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44783</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>45328</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45328</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>44853</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>45758</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45461</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45860</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>45860</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>45156</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>45715</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>44746</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>45975</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>45866</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>45715</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>45176</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         <v>45485</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>44888</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>45161</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45161</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45264</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>45237</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>44908</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>45706</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>45874</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44813</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>45224</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>45715</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>45715</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>45719</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>45875</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>45714</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30923,7 +30923,7 @@
         <v>45714</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>44846</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>44846</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>45819</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>45358</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>44945</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31376,7 +31376,7 @@
         <v>45842</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>45008</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>45981</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>45762</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>45243</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>45671</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>45334</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>44630</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>46098</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>46100</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45209</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44851</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>45160</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>45197</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>45173</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>45985</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>45985</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>45238</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32695,7 +32695,7 @@
         <v>45072</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>46107</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>46107</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>46107</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>46107</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>46107</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>45418</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>45068</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>46106</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>46106</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>45097</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>44848</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>45741</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45071</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45532</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>45111</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>44987</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45992</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45992</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>45992</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>45991</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>46112</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>46113</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>46113</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>46113</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>44908</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>45741</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34736,7 +34736,7 @@
         <v>45391</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>46127</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45576</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>46132</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         <v>44739</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>44539</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45628</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45842</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>44939</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>45882</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45758</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45086</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>45091</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45894</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>46009</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>46009</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>46013</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>46014</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36070,7 +36070,7 @@
         <v>46013</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>45051</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>44789</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36289,7 +36289,7 @@
         <v>45411</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>45082</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>45086</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36508,7 +36508,7 @@
         <v>44925</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>45251</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>46034</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>46034</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36800,7 +36800,7 @@
         <v>45078</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>46034</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>45154</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>44516</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>45818</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>46031</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45278</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>46037</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>46038</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>46037</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>46037</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>44746</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>44781</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>44781</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>45337</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>45680</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>45201</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>44974</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38129,7 +38129,7 @@
         <v>45882</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>46045</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>46045</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>45281</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44949</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45713</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>46048</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>46048</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45057</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>45253</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>46049</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45286</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>46056</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>44991</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>46146</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>46069</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>46071</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39380,7 +39380,7 @@
         <v>46013</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>46037</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>45996</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39599,7 +39599,7 @@
         <v>46162</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>46163</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>46163</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>46163</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>46163</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>46163</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>46163</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>46163</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45916</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>46175</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>46174</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>46175</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>46178</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>46178</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>46182</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>46184</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>46184</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>46184</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>46184</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>46188</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>46197</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>46197</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>46197</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>46199</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>46079</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>46202</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>46209</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>46212</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>46209</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>46209</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41809,7 +41809,7 @@
         <v>46212</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>46209</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>45770</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42038,7 +42038,7 @@
         <v>46272</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>46273</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42184,7 +42184,7 @@
         <v>46274</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42257,7 +42257,7 @@
         <v>46281</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>46034</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>46281</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>46283</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>46196</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>46247</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>46247</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42778,7 +42778,7 @@
         <v>46247</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>46289</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>46289</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43002,7 +43002,7 @@
         <v>46252</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43075,7 +43075,7 @@
         <v>46297</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43153,7 +43153,7 @@
         <v>46297</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>46254</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         <v>45877</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>46255</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>46255</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>46255</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>46255</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>46247</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>46297</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>46300</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>46255</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43966,7 +43966,7 @@
         <v>46294</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>46255</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44112,7 +44112,7 @@
         <v>46259</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>46258</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>45334</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>46034</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45911</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
         <v>46304</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44555,7 +44555,7 @@
         <v>46303</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>46303</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>46260</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>46289</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44862,7 +44862,7 @@
         <v>46183</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>45349</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45008,7 +45008,7 @@
         <v>45349</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45081,7 +45081,7 @@
         <v>45349</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45349</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>45100</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>45100</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>45349</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>45103</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45519,7 +45519,7 @@
         <v>45628</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45592,7 +45592,7 @@
         <v>45349</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45665,7 +45665,7 @@
         <v>45349</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45349</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45042</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>45349</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>45100</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46030,7 +46030,7 @@
         <v>45155</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45770</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45741</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>45712</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45707</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>45804</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45916</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45940</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46629,7 +46629,7 @@
         <v>46121</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46702,7 +46702,7 @@
         <v>46154</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>46166</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>46190</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>46190</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>46153</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>46210</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>

--- a/Översikt EKSJÖ.xlsx
+++ b/Översikt EKSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45013</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45204</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45110</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>45712</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45460</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46135</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45411</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>45285</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>45574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45764</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>44888</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>46297</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>45349</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45122</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45349</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44649</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>44851</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>44504</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>44544</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45369</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45334</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>44854</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>45328</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>45898</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45422</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45330</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>44928</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>45954</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>45666</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44956</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>45975</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>45176</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>45161</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>46106</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45204</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>44958</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>46163</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>46163</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>46283</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>46297</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>46302</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>45553</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>45453</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>45195</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>45707</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>45954</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>44889</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>44781</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44873</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44827</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>44546</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44753</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>44620</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>44790</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44792</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>44482</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>44525</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>44572</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>44573</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>44496</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>44853</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>44746</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>44650</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44873</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44512</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>44845</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>44655</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>44623</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>44782</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>44739</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>44598</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>44552</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>44490</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>44616</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44522</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44610</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44701</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>44748</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44480</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>44861</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>44498</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44746</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>44516</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44739</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44883</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>44847</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44817</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44592</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44523</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44582</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>44616</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>45355</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>44748</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>44630</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>44879</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>45659</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>45762</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>44809</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44480</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>44616</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44831</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>45757</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45370</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>45222</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44991</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>45075</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>45096</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>45152</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>44925</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45716</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>45184</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>45096</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>45049</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>45245</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>44940</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44941</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45334</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45334</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>45214</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>45204</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>44834</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>45097</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>44481</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>45300</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>45212</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>45092</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>45512</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>45649</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>45334</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>45370</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>45141</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>44846</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>44846</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>44966</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>45054</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>45719</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>45076</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>44953</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>45391</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>44846</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>45232</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44845</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45300</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>44803</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>45147</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45208</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>45107</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>44925</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>45561</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>45232</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>45533</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>44974</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>45373</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>44903</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>45533</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>45601</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44865</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45308</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45837</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>45154</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>45463</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45161</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>44917</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>45617</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>45845</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>44942</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>45840</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45537</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45113</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>44580</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>45334</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>45334</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45334</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45825</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45475</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45898</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>44980</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45715</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45677</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>45898</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45723</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45222</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>45195</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45338</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45530</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45575</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45837</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>44861</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45485</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45560</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>44511</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45600</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>45770</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45908</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45426</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45468</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45911</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45533</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>45911</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>45911</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45777</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45777</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45315</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>44600</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45911</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45911</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45664</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>45779</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>45637</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>45916</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>44909</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>45544</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>44609</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>44490</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>45537</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>45251</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>45558</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18834,7 +18834,7 @@
         <v>45161</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>45175</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>45344</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>45216</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>45706</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>45786</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45218</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>44574</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>45402</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>45635</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>45924</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>45790</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45705</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>45071</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>45530</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45513</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45924</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45523</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>44999</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44999</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>45329</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>45204</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>45791</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>45791</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44888</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>45408</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>45579</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45706</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>45714</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20966,7 +20966,7 @@
         <v>45714</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>45714</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>45714</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45345</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45741</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>45728</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>45727</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45743</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45741</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>45743</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>44581</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>45372</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21872,7 +21872,7 @@
         <v>45741</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45741</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>45726</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>44615</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>44974</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44623</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45624</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45384</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45576</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>45173</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>45533</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45078</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45737</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>44928</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45204</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45364</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45911</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45524</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45686</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>44701</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45677</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45091</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45251</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>44713</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>45463</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>45771</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45940</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45176</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45239</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>45811</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45231</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45944</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>45946</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45076</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45162</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>44803</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>45944</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>45715</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44909</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45232</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45161</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45819</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45628</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>45420</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45819</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45086</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>45826</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45223</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45666</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45523</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45523</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45195</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>45195</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>45945</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45954</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>45954</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>45954</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>45003</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26171,7 +26171,7 @@
         <v>45175</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>45632</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>45680</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>45560</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44719</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>45036</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>44685</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>45236</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>45707</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>45365</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>45096</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>45096</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44908</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45839</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45841</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>45841</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45114</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45842</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45972</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>45845</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>45972</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45971</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45842</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>45239</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>45631</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45315</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>44974</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>45695</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45975</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45785</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45314</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45314</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45463</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44783</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>45328</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45328</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>44853</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>45758</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45461</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45860</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>45860</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>45156</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>45715</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>44746</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>45975</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>45866</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>45715</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>45176</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         <v>45485</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>44888</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>45161</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45161</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45264</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>45237</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>44908</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>45706</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>45874</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44813</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>45224</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>45715</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>45715</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>45719</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>45875</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>45714</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30923,7 +30923,7 @@
         <v>45714</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>44846</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>44846</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>45819</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>45358</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>44945</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31376,7 +31376,7 @@
         <v>45842</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>45008</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>45981</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>45762</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>45243</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>45671</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>45334</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>44630</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>46098</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>46100</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45209</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44851</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>45160</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>45197</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>45173</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>45985</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>45985</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>45238</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32695,7 +32695,7 @@
         <v>45072</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>46107</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>46107</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>46107</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>46107</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>46107</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>45418</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>45068</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>46106</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>46106</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>45097</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>44848</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>45741</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45071</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45532</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>45111</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>44987</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45992</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45992</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>45992</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>45991</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>46112</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>46113</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>46113</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>46113</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>44908</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>45741</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34736,7 +34736,7 @@
         <v>45391</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>46127</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45576</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>46132</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         <v>44739</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>44539</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45628</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45842</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>44939</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>45882</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45758</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45086</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>45091</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45894</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>46009</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>46009</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>46013</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>46014</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36070,7 +36070,7 @@
         <v>46013</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>45051</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>44789</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36289,7 +36289,7 @@
         <v>45411</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>45082</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>45086</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36508,7 +36508,7 @@
         <v>44925</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>45251</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>46034</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>46034</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36800,7 +36800,7 @@
         <v>45078</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>46034</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>45154</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>44516</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>45818</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>46031</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45278</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>46037</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>46038</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>46037</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>46037</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>44746</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>44781</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>44781</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>45337</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>45680</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>45201</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>44974</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38129,7 +38129,7 @@
         <v>45882</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>46045</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>46045</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>45281</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44949</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45713</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>46048</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>46048</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45057</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>45253</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>46049</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45286</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>46056</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>44991</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>46146</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>46069</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>46071</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39380,7 +39380,7 @@
         <v>46013</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>46037</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>45996</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39599,7 +39599,7 @@
         <v>46162</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>46163</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>46163</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>46163</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>46163</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>46163</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>46163</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>46163</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45916</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>46175</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>46174</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>46175</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>46178</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>46178</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>46182</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>46184</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>46184</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>46184</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>46184</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>46188</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>46197</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>46197</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>46197</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>46199</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>46079</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>46202</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>46209</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>46212</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>46209</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>46209</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41809,7 +41809,7 @@
         <v>46212</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>46209</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>45770</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42038,7 +42038,7 @@
         <v>46272</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>46273</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42184,7 +42184,7 @@
         <v>46274</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42257,7 +42257,7 @@
         <v>46281</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>46034</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>46281</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>46283</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>46196</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>46247</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>46247</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42778,7 +42778,7 @@
         <v>46247</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>46289</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>46289</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43002,7 +43002,7 @@
         <v>46252</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43075,7 +43075,7 @@
         <v>46297</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43153,7 +43153,7 @@
         <v>46297</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>46254</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         <v>45877</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>46255</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>46255</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>46255</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>46255</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>46247</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>46297</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>46300</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>46255</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43966,7 +43966,7 @@
         <v>46294</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>46255</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44112,7 +44112,7 @@
         <v>46259</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>46258</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>45334</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>46034</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45911</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
         <v>46304</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44555,7 +44555,7 @@
         <v>46303</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>46303</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>46260</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>46289</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44862,7 +44862,7 @@
         <v>46183</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>45349</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45008,7 +45008,7 @@
         <v>45349</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45081,7 +45081,7 @@
         <v>45349</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45349</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>45100</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>45100</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>45349</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>45103</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45519,7 +45519,7 @@
         <v>45628</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45592,7 +45592,7 @@
         <v>45349</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45665,7 +45665,7 @@
         <v>45349</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45349</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45042</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>45349</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>45100</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46030,7 +46030,7 @@
         <v>45155</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45770</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45741</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>45712</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45707</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>45804</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45916</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45940</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46629,7 +46629,7 @@
         <v>46121</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46702,7 +46702,7 @@
         <v>46154</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>46166</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>46190</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>46190</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>46153</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>46210</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>

--- a/Översikt EKSJÖ.xlsx
+++ b/Översikt EKSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45013</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45204</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45110</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>45712</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45460</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46135</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45764</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45285</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45411</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>45574</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>44888</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>46297</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>46310</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45349</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>45122</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45349</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>44649</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>44487</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>44504</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44544</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45328</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>44956</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45204</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>45176</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>44854</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>45898</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>45954</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45975</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>46163</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>46163</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45369</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>45161</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>46106</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>44928</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>44958</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>45422</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>45334</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>46297</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46302</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>46307</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45330</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>46283</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>45666</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>45553</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>45453</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>45195</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>45707</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45954</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44781</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44889</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>44873</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>44827</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44546</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>44753</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>44620</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>44790</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>44792</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>44525</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>44572</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>44573</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44496</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>44746</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>44853</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>44650</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>44873</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>44512</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>44845</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44655</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44623</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>44782</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>44739</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>44598</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>44490</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>44552</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>44498</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>44861</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44746</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44516</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>44592</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>44616</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44701</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>44739</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>44883</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>44523</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>44748</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>44847</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>44522</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>44610</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>44817</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>44582</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>44616</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>44630</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44879</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>44616</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>44831</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>44748</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44980</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45078</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45575</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>44909</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>44942</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>44861</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>45003</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>44903</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>45152</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>44809</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>44940</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>44941</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>45057</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>44949</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>45051</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>45264</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>45243</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44925</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>45344</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>45345</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>45523</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>45544</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>45092</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>44908</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45408</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>45281</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>45097</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>45237</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45533</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>45355</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>45715</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>45715</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>45530</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>45558</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>45680</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>45161</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
         <v>45161</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>45485</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>45204</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>45076</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44888</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>45231</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45716</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>45096</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45096</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>45463</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>45147</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>45719</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>45601</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>45686</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>45532</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>45714</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>45251</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>44834</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45664</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>44574</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>45418</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45485</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>44888</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45078</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44953</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>44803</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>45204</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>45176</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>45631</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>45245</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>45358</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45758</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45463</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>45162</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>44580</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>45097</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15287,7 +15287,7 @@
         <v>45216</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>45008</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>45741</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45741</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>45315</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>45036</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>45328</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44511</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>45184</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>44781</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>44781</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45232</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>45837</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>45840</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>45845</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45842</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>45825</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>45758</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45770</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45882</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45882</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45628</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>45898</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>45251</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45898</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>45232</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>44991</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>45223</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45201</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>45195</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>45086</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>45837</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45334</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45908</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>44991</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45364</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44945</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45911</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45911</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45911</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45911</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45911</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>45338</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45757</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45222</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45222</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45916</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45391</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45334</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>46146</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>45924</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>45924</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45334</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45334</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>44746</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>45195</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>45195</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>44928</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>45071</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>45173</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45911</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>45161</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>45475</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45334</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>45940</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>45463</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>46037</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45373</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>45337</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>46013</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>45944</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44987</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>45946</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>45677</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45944</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45666</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45680</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45945</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45954</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>44630</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45286</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45954</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45954</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>45512</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>45086</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>45384</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>45971</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>45996</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>45315</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21869,7 +21869,7 @@
         <v>45173</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>46162</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>45972</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>46163</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45972</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>46163</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45975</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>45975</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45513</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>46163</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>46163</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>46163</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>46163</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>46163</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45617</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>45706</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>45981</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>44516</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>45576</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>44917</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>45985</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>44846</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>45985</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>44846</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>45365</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>45916</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>44925</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45239</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45114</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45992</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45402</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45713</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>45992</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>45176</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         <v>45314</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>45314</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45991</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>45992</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>45091</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>45197</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>45659</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>45141</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>46009</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>46009</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>46174</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>46013</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45232</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>46013</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>46014</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45175</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>45086</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>46175</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>45238</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>46031</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45533</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>44783</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>46175</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>46034</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>46034</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>46034</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>46037</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>46178</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>46037</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>46037</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>46038</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26664,7 +26664,7 @@
         <v>45533</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26737,7 +26737,7 @@
         <v>46178</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45054</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>46045</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>46045</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>46048</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>45628</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>46048</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>46049</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>44739</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>45113</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>46182</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45523</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>45523</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>45600</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>45533</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27837,7 +27837,7 @@
         <v>46056</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         <v>46184</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>45049</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>44853</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>46184</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>45714</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>45714</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>44925</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>46184</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>46184</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45212</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>46069</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>45072</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>44974</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>46071</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>46188</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>44685</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29103,7 +29103,7 @@
         <v>44846</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>44813</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>45420</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>45426</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>44803</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45251</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>45677</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>45075</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>44974</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>46098</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44846</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>44846</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>45468</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>46100</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>44713</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>45308</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>46106</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>46106</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45723</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>46107</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>46107</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>46107</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>46107</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>46107</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30900,7 +30900,7 @@
         <v>45154</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>46197</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31046,7 +31046,7 @@
         <v>45328</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>46112</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>46113</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>46197</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>46197</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>46113</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>46113</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>44908</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>46079</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>46202</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>44615</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>46199</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44909</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>46127</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>45161</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         <v>46132</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>45224</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>45154</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>45894</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45706</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>45719</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45818</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>44701</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>45161</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32818,7 +32818,7 @@
         <v>45082</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32891,7 +32891,7 @@
         <v>45649</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>46209</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>46209</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33120,7 +33120,7 @@
         <v>46209</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>46209</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>45096</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         <v>46212</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>46212</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>45770</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33573,7 +33573,7 @@
         <v>45236</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>45537</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33724,7 +33724,7 @@
         <v>45278</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>44966</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45160</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>46273</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>45370</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         <v>45068</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>46272</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>44539</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>46274</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45253</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>44845</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>44789</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>45239</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34678,7 +34678,7 @@
         <v>45370</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>45334</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>44865</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>45107</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>45204</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>45714</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35131,7 +35131,7 @@
         <v>46281</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35204,7 +35204,7 @@
         <v>44974</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>45560</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>45576</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35428,7 +35428,7 @@
         <v>44490</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45076</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35574,7 +35574,7 @@
         <v>46281</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45096</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>45372</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>44623</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35871,7 +35871,7 @@
         <v>45156</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>45071</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>44908</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36090,7 +36090,7 @@
         <v>45391</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>46196</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>44581</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45111</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>44600</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>45715</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         <v>45411</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>45214</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36679,7 +36679,7 @@
         <v>45300</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>44746</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>46034</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36898,7 +36898,7 @@
         <v>45300</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>46289</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37044,7 +37044,7 @@
         <v>45632</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37117,7 +37117,7 @@
         <v>45208</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37190,7 +37190,7 @@
         <v>45218</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>44848</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37336,7 +37336,7 @@
         <v>46289</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>45537</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>45714</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45714</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>45715</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37721,7 +37721,7 @@
         <v>45715</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>45715</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>46247</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37950,7 +37950,7 @@
         <v>44851</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38023,7 +38023,7 @@
         <v>45707</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>46247</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>46247</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>45329</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38325,7 +38325,7 @@
         <v>45635</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
         <v>45334</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>44939</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>45561</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>46252</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>44719</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>46297</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45762</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38924,7 +38924,7 @@
         <v>46247</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>46297</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45671</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39143,7 +39143,7 @@
         <v>46254</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>46297</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45877</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>44609</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>46034</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>44999</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>44999</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>45209</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45777</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>46255</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39878,7 +39878,7 @@
         <v>45777</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>46255</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>46258</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40107,7 +40107,7 @@
         <v>45779</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>45334</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>46300</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40336,7 +40336,7 @@
         <v>45637</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40409,7 +40409,7 @@
         <v>46255</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>46255</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>46255</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40633,7 +40633,7 @@
         <v>45706</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40706,7 +40706,7 @@
         <v>46255</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>45911</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
         <v>46260</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>45786</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>46183</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41071,7 +41071,7 @@
         <v>46259</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41144,7 +41144,7 @@
         <v>45705</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>45175</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41290,7 +41290,7 @@
         <v>45530</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41363,7 +41363,7 @@
         <v>45790</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>46303</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>46303</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45579</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41665,7 +41665,7 @@
         <v>45791</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>45791</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41811,7 +41811,7 @@
         <v>46304</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>46283</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>45743</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45624</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>45743</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42176,7 +42176,7 @@
         <v>45741</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42254,7 +42254,7 @@
         <v>45726</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>45741</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45741</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45728</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>45741</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45727</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>46309</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>46308</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>45737</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>46308</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45524</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>46309</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43170,7 +43170,7 @@
         <v>46309</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45811</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>45091</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45771</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43467,7 +43467,7 @@
         <v>46311</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>46311</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>46289</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45819</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>46311</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>45819</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>46311</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44003,7 +44003,7 @@
         <v>46310</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>46294</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>46310</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>45826</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>45560</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44373,7 +44373,7 @@
         <v>45839</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45841</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45841</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>45842</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>45845</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>45842</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>45785</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>44974</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44967,7 +44967,7 @@
         <v>45695</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45461</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>45860</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45191,7 +45191,7 @@
         <v>45860</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45866</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45337,7 +45337,7 @@
         <v>45874</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45410,7 +45410,7 @@
         <v>45875</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45483,7 +45483,7 @@
         <v>45819</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45842</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>45762</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45702,7 +45702,7 @@
         <v>45349</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45775,7 +45775,7 @@
         <v>45349</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45848,7 +45848,7 @@
         <v>45349</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>45349</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45994,7 +45994,7 @@
         <v>45100</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>45100</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>45349</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46213,7 +46213,7 @@
         <v>45103</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>45628</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46359,7 +46359,7 @@
         <v>45349</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46432,7 +46432,7 @@
         <v>45349</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46505,7 +46505,7 @@
         <v>45349</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46578,7 +46578,7 @@
         <v>45042</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>45349</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45100</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>45155</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>45770</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>45741</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>45712</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>45707</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45804</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>45916</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45940</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>46121</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>46154</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>46166</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>46190</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>46190</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>46210</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>46153</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
         <v>46311</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>

--- a/Översikt EKSJÖ.xlsx
+++ b/Översikt EKSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45013</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45204</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45110</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>45712</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45460</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46135</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45764</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45285</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45411</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>45574</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>44888</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>46297</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>46310</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45349</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>45122</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45349</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>44649</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>44487</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>44504</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44544</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45328</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>44956</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45204</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>45176</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>44854</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>45898</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>45954</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45975</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>46163</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>46163</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45369</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>45161</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>46106</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>44928</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>44958</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>45422</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>45334</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>46297</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46302</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>46307</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45330</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>46283</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>45666</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>45553</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>45453</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>45195</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>45707</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45954</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44781</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44889</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>44873</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>44827</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44546</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>44753</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>44620</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>44790</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>44792</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>44525</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>44572</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>44573</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44496</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>44746</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>44853</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>44650</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>44873</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>44512</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>44845</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44655</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44623</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>44782</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>44739</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>44598</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>44490</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>44552</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>44498</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>44861</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44746</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44516</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>44592</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>44616</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44701</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>44739</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>44883</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>44523</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>44748</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>44847</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>44522</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>44610</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>44817</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>44582</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>44616</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>44630</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44879</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>44616</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>44831</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>44748</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44980</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45078</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45575</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>44909</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>44942</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>44861</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>45003</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>44903</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>45152</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>44809</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>44940</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>44941</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>45057</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>44949</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>45051</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>45264</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>45243</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44925</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>45344</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>45345</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>45523</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>45544</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>45092</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>44908</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45408</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>45281</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>45097</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>45237</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45533</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>45355</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>45715</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>45715</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>45530</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>45558</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>45680</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>45161</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
         <v>45161</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>45485</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>45204</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>45076</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44888</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>45231</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45716</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>45096</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45096</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>45463</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>45147</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>45719</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>45601</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>45686</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>45532</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>45714</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>45251</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>44834</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45664</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>44574</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>45418</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45485</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>44888</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45078</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44953</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>44803</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>45204</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>45176</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>45631</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>45245</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>45358</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45758</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45463</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>45162</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>44580</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>45097</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15287,7 +15287,7 @@
         <v>45216</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>45008</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>45741</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45741</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>45315</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>45036</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>45328</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44511</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>45184</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>44781</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>44781</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45232</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>45837</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>45840</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>45845</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45842</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>45825</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>45758</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45770</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45882</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45882</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45628</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>45898</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>45251</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45898</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>45232</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>44991</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>45223</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45201</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>45195</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>45086</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>45837</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45334</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45908</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>44991</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45364</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44945</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45911</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45911</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45911</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45911</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45911</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>45338</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45757</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45222</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45222</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45916</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45391</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45334</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>46146</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>45924</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>45924</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45334</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45334</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>44746</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>45195</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>45195</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>44928</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>45071</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>45173</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45911</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>45161</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>45475</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45334</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>45940</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>45463</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>46037</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45373</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>45337</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>46013</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>45944</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44987</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>45946</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>45677</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45944</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45666</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45680</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45945</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45954</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>44630</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45286</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45954</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45954</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>45512</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>45086</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>45384</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>45971</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>45996</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>45315</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21869,7 +21869,7 @@
         <v>45173</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>46162</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>45972</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>46163</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45972</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>46163</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45975</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>45975</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45513</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>46163</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>46163</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>46163</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>46163</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>46163</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45617</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>45706</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>45981</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>44516</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>45576</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>44917</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>45985</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>44846</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>45985</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>44846</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>45365</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>45916</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>44925</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45239</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45114</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45992</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45402</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45713</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>45992</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>45176</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         <v>45314</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>45314</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45991</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>45992</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>45091</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>45197</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>45659</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>45141</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>46009</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>46009</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>46174</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>46013</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45232</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>46013</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>46014</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45175</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>45086</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>46175</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>45238</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>46031</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45533</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>44783</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>46175</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>46034</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>46034</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>46034</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>46037</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>46178</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>46037</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>46037</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>46038</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26664,7 +26664,7 @@
         <v>45533</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26737,7 +26737,7 @@
         <v>46178</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45054</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>46045</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>46045</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>46048</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>45628</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>46048</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>46049</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>44739</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>45113</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>46182</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45523</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>45523</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>45600</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>45533</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27837,7 +27837,7 @@
         <v>46056</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         <v>46184</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>45049</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>44853</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>46184</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>45714</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>45714</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>44925</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>46184</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>46184</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45212</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>46069</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>45072</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>44974</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>46071</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>46188</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>44685</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29103,7 +29103,7 @@
         <v>44846</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>44813</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>45420</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>45426</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>44803</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45251</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>45677</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>45075</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>44974</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>46098</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44846</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>44846</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>45468</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>46100</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>44713</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>45308</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>46106</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>46106</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45723</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>46107</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>46107</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>46107</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>46107</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>46107</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30900,7 +30900,7 @@
         <v>45154</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>46197</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31046,7 +31046,7 @@
         <v>45328</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>46112</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>46113</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>46197</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>46197</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>46113</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>46113</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>44908</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>46079</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>46202</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>44615</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>46199</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44909</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>46127</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>45161</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         <v>46132</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>45224</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>45154</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>45894</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45706</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>45719</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45818</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>44701</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>45161</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32818,7 +32818,7 @@
         <v>45082</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32891,7 +32891,7 @@
         <v>45649</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>46209</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>46209</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33120,7 +33120,7 @@
         <v>46209</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>46209</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>45096</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         <v>46212</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>46212</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>45770</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33573,7 +33573,7 @@
         <v>45236</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>45537</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33724,7 +33724,7 @@
         <v>45278</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>44966</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45160</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>46273</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>45370</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         <v>45068</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>46272</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>44539</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>46274</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45253</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>44845</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>44789</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>45239</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34678,7 +34678,7 @@
         <v>45370</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>45334</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>44865</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>45107</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>45204</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>45714</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35131,7 +35131,7 @@
         <v>46281</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35204,7 +35204,7 @@
         <v>44974</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>45560</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>45576</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35428,7 +35428,7 @@
         <v>44490</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45076</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35574,7 +35574,7 @@
         <v>46281</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45096</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>45372</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>44623</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35871,7 +35871,7 @@
         <v>45156</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>45071</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>44908</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36090,7 +36090,7 @@
         <v>45391</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>46196</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>44581</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45111</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>44600</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>45715</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         <v>45411</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>45214</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36679,7 +36679,7 @@
         <v>45300</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>44746</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>46034</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36898,7 +36898,7 @@
         <v>45300</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>46289</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37044,7 +37044,7 @@
         <v>45632</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37117,7 +37117,7 @@
         <v>45208</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37190,7 +37190,7 @@
         <v>45218</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>44848</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37336,7 +37336,7 @@
         <v>46289</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>45537</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>45714</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45714</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>45715</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37721,7 +37721,7 @@
         <v>45715</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>45715</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>46247</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37950,7 +37950,7 @@
         <v>44851</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38023,7 +38023,7 @@
         <v>45707</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>46247</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>46247</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>45329</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38325,7 +38325,7 @@
         <v>45635</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
         <v>45334</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>44939</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>45561</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>46252</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>44719</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>46297</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45762</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38924,7 +38924,7 @@
         <v>46247</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>46297</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45671</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39143,7 +39143,7 @@
         <v>46254</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>46297</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45877</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>44609</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>46034</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>44999</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>44999</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>45209</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45777</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>46255</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39878,7 +39878,7 @@
         <v>45777</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>46255</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>46258</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40107,7 +40107,7 @@
         <v>45779</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>45334</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>46300</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40336,7 +40336,7 @@
         <v>45637</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40409,7 +40409,7 @@
         <v>46255</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>46255</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>46255</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40633,7 +40633,7 @@
         <v>45706</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40706,7 +40706,7 @@
         <v>46255</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>45911</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
         <v>46260</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>45786</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>46183</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41071,7 +41071,7 @@
         <v>46259</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41144,7 +41144,7 @@
         <v>45705</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>45175</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41290,7 +41290,7 @@
         <v>45530</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41363,7 +41363,7 @@
         <v>45790</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>46303</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>46303</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45579</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41665,7 +41665,7 @@
         <v>45791</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>45791</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41811,7 +41811,7 @@
         <v>46304</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>46283</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>45743</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45624</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>45743</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42176,7 +42176,7 @@
         <v>45741</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42254,7 +42254,7 @@
         <v>45726</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>45741</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45741</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45728</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>45741</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45727</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>46309</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>46308</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>45737</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>46308</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45524</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>46309</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43170,7 +43170,7 @@
         <v>46309</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45811</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>45091</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45771</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43467,7 +43467,7 @@
         <v>46311</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>46311</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>46289</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45819</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>46311</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>45819</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>46311</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44003,7 +44003,7 @@
         <v>46310</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>46294</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>46310</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>45826</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>45560</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44373,7 +44373,7 @@
         <v>45839</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45841</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45841</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>45842</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>45845</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>45842</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>45785</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>44974</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44967,7 +44967,7 @@
         <v>45695</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45461</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>45860</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45191,7 +45191,7 @@
         <v>45860</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45866</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45337,7 +45337,7 @@
         <v>45874</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45410,7 +45410,7 @@
         <v>45875</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45483,7 +45483,7 @@
         <v>45819</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45842</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>45762</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45702,7 +45702,7 @@
         <v>45349</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45775,7 +45775,7 @@
         <v>45349</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45848,7 +45848,7 @@
         <v>45349</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>45349</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45994,7 +45994,7 @@
         <v>45100</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>45100</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>45349</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46213,7 +46213,7 @@
         <v>45103</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>45628</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46359,7 +46359,7 @@
         <v>45349</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46432,7 +46432,7 @@
         <v>45349</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46505,7 +46505,7 @@
         <v>45349</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46578,7 +46578,7 @@
         <v>45042</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>45349</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45100</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>45155</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>45770</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>45741</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>45712</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>45707</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45804</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>45916</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45940</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>46121</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>46154</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>46166</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>46190</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>46190</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>46210</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>46153</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
         <v>46311</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>

--- a/Översikt EKSJÖ.xlsx
+++ b/Översikt EKSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45013</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45204</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45110</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>45712</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45460</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46135</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45411</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>45285</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>45574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>46297</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>46310</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>44888</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>45764</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45349</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>45122</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45349</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>44649</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>44504</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44544</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45334</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>45898</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>44854</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>46163</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>46163</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>44958</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>45369</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>45954</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>45975</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45330</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45328</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>46297</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45666</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>46106</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>46307</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>46283</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>46302</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>44928</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>45422</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>44956</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>45176</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>45161</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>45204</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>45553</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>45453</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>45195</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>45707</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>45954</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>44889</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>44873</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>44827</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>44781</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44546</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>44753</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>44620</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>44790</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>44792</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>44525</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>44572</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>44496</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>44573</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>44853</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>44650</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44746</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>44873</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>44512</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>44845</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>44655</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>44623</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>44782</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>44739</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44598</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>44552</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44498</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>44861</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>44746</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>44516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>44592</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>44616</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>44701</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>44883</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>44739</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>44523</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44748</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>44847</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>44522</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>44610</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44817</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44582</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>44616</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>44539</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>44748</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>44630</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>44879</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>45837</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45232</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44616</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>44831</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>44991</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>45845</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>45840</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>45716</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
         <v>45184</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45049</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>45334</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>44939</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>45334</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>45825</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>44834</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45086</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>45512</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45334</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>45091</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>45898</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>45719</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>45076</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>45232</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>45898</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45195</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45051</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45355</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45837</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44789</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45411</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45082</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45086</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45908</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44925</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>45911</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>45911</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>45911</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>46162</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>45911</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>45911</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>46163</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>46163</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>46163</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>45916</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>45078</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>46163</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>45154</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>44516</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>46163</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>46163</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44809</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>46163</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>45278</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>45924</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44746</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44781</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>44781</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>45924</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>45916</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>45337</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>45680</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>45201</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>44974</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>45281</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>46175</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44949</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45713</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>46174</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>45057</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>45253</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>45911</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>45286</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>45940</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>45659</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>45762</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>46175</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>45096</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>45245</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>45944</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>45370</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45300</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45946</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>45075</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45096</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45370</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>46178</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45152</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>44846</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44846</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>45944</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44925</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>44940</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>44941</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         <v>46178</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>45945</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>45954</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>45954</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>46182</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>45214</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>45204</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>45954</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>46184</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>45212</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>46184</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>46184</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>45649</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>46184</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>46188</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>45141</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>45054</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         <v>44846</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>44845</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45300</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45972</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>44803</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>45972</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>45971</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>45208</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>45107</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>44925</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>46197</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>45373</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>46197</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>45601</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>46197</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>45975</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>45975</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>46199</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>46079</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>45308</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45463</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>46202</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45161</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45617</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45981</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>44580</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45985</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45533</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>45475</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>45985</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>44974</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>45715</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>45677</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>45723</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>45222</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>46209</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45338</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45992</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>45992</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>46212</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45575</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>46209</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45992</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21004,7 +21004,7 @@
         <v>46209</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>45991</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>46212</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>46209</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>44903</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45533</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45770</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45600</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45770</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45426</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45777</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45777</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45779</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>45637</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>44865</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>45175</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>46009</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>45706</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         <v>46009</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>46013</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>46014</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>46013</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>45786</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>45790</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>45705</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>45530</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>46281</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>46034</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>46034</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>46034</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>46034</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>45791</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23390,7 +23390,7 @@
         <v>46281</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>46031</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>45791</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>45579</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>46037</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>46038</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>46196</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>46037</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>46037</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45741</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>45728</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>45727</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>45743</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>45741</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>45743</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>45741</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>45741</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>46045</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>46045</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>45154</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>45726</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>46048</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>46048</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>45624</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>46247</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>46049</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>46247</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>46247</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>45737</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>46056</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45524</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>46289</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>46289</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45091</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45771</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>45811</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44942</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>46069</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>46071</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45819</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45819</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45826</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>46252</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>46297</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>45560</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>46254</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>46255</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>46255</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>46255</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>46255</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45113</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>46247</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>46297</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>46300</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>46255</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>45839</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45841</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>45841</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>45334</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>45334</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>45842</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>46255</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>46098</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>45845</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45842</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>46100</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>46259</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>46258</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>45334</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>44974</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>46107</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>46107</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>46107</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>46107</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>46107</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>45695</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>45785</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>46106</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>46106</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>45461</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>46034</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>46112</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>46113</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>46113</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>45860</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         <v>45860</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>46113</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>45530</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45911</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>46304</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44861</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>45866</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>45485</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>46303</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>46303</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>46260</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>46183</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45874</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>46127</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>45875</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>45819</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>46132</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30991,7 +30991,7 @@
         <v>45842</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>46308</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>45762</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>46283</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31288,7 +31288,7 @@
         <v>45533</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>44600</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45628</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>45842</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>44909</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>46308</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>45882</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31804,7 +31804,7 @@
         <v>45544</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31877,7 +31877,7 @@
         <v>45758</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>46309</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>46310</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32106,7 +32106,7 @@
         <v>45537</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32179,7 +32179,7 @@
         <v>46309</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>46310</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>45558</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>45894</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>46309</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32554,7 +32554,7 @@
         <v>45216</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>45218</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>44574</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32773,7 +32773,7 @@
         <v>46311</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>46311</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>46314</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>45251</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>46297</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>45513</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>46294</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>46311</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33377,7 +33377,7 @@
         <v>45818</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>46314</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>46311</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>46273</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>44888</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45408</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>46316</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>46272</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>46315</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>46315</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45882</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>46315</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>46317</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>46317</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>46274</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>46318</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>46317</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>46318</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>46317</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>45372</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>44991</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>44974</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>44623</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>46318</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45384</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>46289</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>46146</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>45576</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>45533</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>44928</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>45364</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>44701</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>45251</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>44713</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>45463</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>46013</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36075,7 +36075,7 @@
         <v>45076</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>46037</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36221,7 +36221,7 @@
         <v>44803</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45715</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>44909</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36445,7 +36445,7 @@
         <v>45996</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>45628</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45086</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>45003</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36737,7 +36737,7 @@
         <v>45632</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>44719</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36883,7 +36883,7 @@
         <v>45036</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>45365</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45096</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>45096</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>45114</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>45631</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>44783</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>44853</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45156</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37550,7 +37550,7 @@
         <v>45715</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>45485</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>45161</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>45161</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>45237</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45706</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44813</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>45224</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>45715</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>45715</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38295,7 +38295,7 @@
         <v>45719</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>45714</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         <v>45714</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38524,7 +38524,7 @@
         <v>44945</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>45008</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>45671</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38748,7 +38748,7 @@
         <v>45334</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38826,7 +38826,7 @@
         <v>45197</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>45173</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38972,7 +38972,7 @@
         <v>45238</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39045,7 +39045,7 @@
         <v>45072</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45418</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39191,7 +39191,7 @@
         <v>45068</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39264,7 +39264,7 @@
         <v>45741</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>45071</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>45111</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39488,7 +39488,7 @@
         <v>44908</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>45741</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45757</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>45222</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         <v>45097</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
         <v>45092</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39931,7 +39931,7 @@
         <v>44966</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>44953</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45391</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>45147</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45561</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40306,7 +40306,7 @@
         <v>44917</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40379,7 +40379,7 @@
         <v>45537</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>45334</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>44980</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40598,7 +40598,7 @@
         <v>45560</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40671,7 +40671,7 @@
         <v>44511</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>45468</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>45315</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45664</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44609</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41036,7 +41036,7 @@
         <v>45251</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>45161</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45344</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>45402</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>45635</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>45071</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>45523</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41547,7 +41547,7 @@
         <v>44999</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44999</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>45329</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45204</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>45706</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>45714</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>45714</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>45714</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45714</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45345</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42302,7 +42302,7 @@
         <v>44581</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42375,7 +42375,7 @@
         <v>44615</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42448,7 +42448,7 @@
         <v>45173</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45078</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42594,7 +42594,7 @@
         <v>45204</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42672,7 +42672,7 @@
         <v>45686</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>45677</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>45176</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>45239</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>45231</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45162</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45232</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>45161</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>45420</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>45223</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>45666</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45523</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43548,7 +43548,7 @@
         <v>45523</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>45195</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43694,7 +43694,7 @@
         <v>45195</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45175</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>45680</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>44685</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43991,7 +43991,7 @@
         <v>45236</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>45707</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>44908</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44215,7 +44215,7 @@
         <v>45239</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44288,7 +44288,7 @@
         <v>45315</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44361,7 +44361,7 @@
         <v>45314</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44434,7 +44434,7 @@
         <v>45314</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45463</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45328</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44653,7 +44653,7 @@
         <v>45328</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45758</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45715</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44882,7 +44882,7 @@
         <v>44746</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44955,7 +44955,7 @@
         <v>45176</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         <v>44888</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45101,7 +45101,7 @@
         <v>45264</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>44908</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45252,7 +45252,7 @@
         <v>44846</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>44846</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45398,7 +45398,7 @@
         <v>45358</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>45243</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>44630</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45209</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45695,7 +45695,7 @@
         <v>44851</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>45160</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45097</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>44848</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>45532</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46060,7 +46060,7 @@
         <v>44987</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>45391</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46206,7 +46206,7 @@
         <v>45576</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46279,7 +46279,7 @@
         <v>44739</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45349</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46425,7 +46425,7 @@
         <v>45349</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46498,7 +46498,7 @@
         <v>45349</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46571,7 +46571,7 @@
         <v>45349</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>45100</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>45100</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>45349</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>45103</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45628</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47009,7 +47009,7 @@
         <v>45349</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
         <v>45349</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>45349</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47228,7 +47228,7 @@
         <v>45042</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45349</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>45100</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45155</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47520,7 +47520,7 @@
         <v>45770</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45741</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45712</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45707</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>45804</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45916</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>45940</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>46121</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         <v>46154</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48192,7 +48192,7 @@
         <v>46166</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>46190</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>46190</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48411,7 +48411,7 @@
         <v>46153</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>46210</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
         <v>46311</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48635,7 +48635,7 @@
         <v>46315</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>

--- a/Översikt EKSJÖ.xlsx
+++ b/Översikt EKSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45013</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45204</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45110</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>45712</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45460</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46135</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45411</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>45285</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>45574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>46297</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>46310</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>44888</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>45764</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45349</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>45122</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45349</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>44649</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>44504</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44544</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45334</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>45898</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>44854</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>46163</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>46163</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>44958</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>45369</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>45954</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>45975</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45330</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45328</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>46297</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45666</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>46106</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>46307</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>46283</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>46302</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>44928</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>45422</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>44956</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>45176</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>45161</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>45204</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>45553</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>45453</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>45195</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>45707</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>45954</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>44889</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>44873</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>44827</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>44781</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44546</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>44753</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>44620</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>44790</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>44792</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>44525</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>44572</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>44496</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>44573</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>44853</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>44650</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44746</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>44873</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>44512</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>44845</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>44655</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>44623</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>44782</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>44739</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44598</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>44552</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44498</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>44861</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>44746</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>44516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>44592</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>44616</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>44701</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>44883</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>44739</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>44523</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44748</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>44847</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>44522</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>44610</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44817</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44582</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>44616</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>44539</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>44748</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>44630</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>44879</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>45837</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45232</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44616</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>44831</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>44991</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>45845</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>45840</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>45716</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
         <v>45184</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45049</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>45334</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>44939</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>45334</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>45825</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>44834</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45086</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>45512</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45334</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>45091</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>45898</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>45719</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>45076</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>45232</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>45898</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45195</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45051</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45355</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45837</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44789</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45411</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45082</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45086</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45908</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44925</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>45911</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>45911</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>45911</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>46162</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>45911</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>45911</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>46163</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>46163</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>46163</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>45916</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>45078</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>46163</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>45154</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>44516</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>46163</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>46163</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44809</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>46163</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>45278</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>45924</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44746</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44781</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>44781</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>45924</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>45916</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>45337</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>45680</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>45201</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>44974</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>45281</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>46175</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44949</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45713</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>46174</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>45057</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>45253</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>45911</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>45286</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>45940</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>45659</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>45762</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>46175</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>45096</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>45245</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>45944</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>45370</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45300</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45946</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>45075</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45096</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45370</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>46178</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45152</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>44846</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44846</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>45944</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44925</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>44940</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>44941</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         <v>46178</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>45945</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>45954</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>45954</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>46182</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>45214</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>45204</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>45954</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>46184</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>45212</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>46184</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>46184</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>45649</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>46184</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>46188</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>45141</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>45054</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         <v>44846</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>44845</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45300</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45972</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>44803</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>45972</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>45971</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>45208</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>45107</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>44925</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>46197</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>45373</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>46197</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>45601</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>46197</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>45975</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>45975</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>46199</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>46079</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>45308</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45463</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>46202</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45161</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45617</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45981</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>44580</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45985</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45533</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>45475</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>45985</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>44974</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>45715</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>45677</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>45723</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>45222</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>46209</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45338</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45992</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>45992</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>46212</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45575</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>46209</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45992</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21004,7 +21004,7 @@
         <v>46209</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>45991</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>46212</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>46209</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>44903</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45533</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45770</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45600</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45770</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45426</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45777</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45777</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45779</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>45637</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>44865</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>45175</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>46009</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>45706</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         <v>46009</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>46013</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>46014</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>46013</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>45786</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>45790</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>45705</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>45530</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>46281</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>46034</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>46034</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>46034</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>46034</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>45791</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23390,7 +23390,7 @@
         <v>46281</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>46031</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>45791</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>45579</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>46037</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>46038</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>46196</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>46037</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>46037</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45741</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>45728</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>45727</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>45743</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>45741</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>45743</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>45741</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>45741</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>46045</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>46045</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>45154</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>45726</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>46048</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>46048</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>45624</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>46247</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>46049</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>46247</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>46247</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>45737</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>46056</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45524</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>46289</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>46289</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45091</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45771</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>45811</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44942</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>46069</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>46071</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45819</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45819</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45826</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>46252</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>46297</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>45560</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>46254</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>46255</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>46255</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>46255</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>46255</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45113</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>46247</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>46297</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>46300</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>46255</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>45839</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45841</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>45841</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>45334</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>45334</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>45842</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>46255</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>46098</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>45845</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45842</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>46100</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>46259</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>46258</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>45334</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>44974</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>46107</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>46107</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>46107</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>46107</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>46107</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>45695</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>45785</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>46106</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>46106</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>45461</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>46034</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>46112</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>46113</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>46113</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>45860</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         <v>45860</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>46113</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>45530</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45911</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>46304</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44861</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>45866</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>45485</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>46303</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>46303</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>46260</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>46183</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45874</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>46127</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>45875</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>45819</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>46132</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30991,7 +30991,7 @@
         <v>45842</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>46308</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>45762</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>46283</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31288,7 +31288,7 @@
         <v>45533</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>44600</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45628</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>45842</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>44909</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>46308</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>45882</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31804,7 +31804,7 @@
         <v>45544</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31877,7 +31877,7 @@
         <v>45758</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>46309</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>46310</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32106,7 +32106,7 @@
         <v>45537</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32179,7 +32179,7 @@
         <v>46309</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>46310</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>45558</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>45894</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>46309</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32554,7 +32554,7 @@
         <v>45216</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>45218</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>44574</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32773,7 +32773,7 @@
         <v>46311</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>46311</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>46314</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>45251</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>46297</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>45513</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>46294</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>46311</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33377,7 +33377,7 @@
         <v>45818</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>46314</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>46311</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>46273</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>44888</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45408</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>46316</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>46272</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>46315</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>46315</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45882</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>46315</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>46317</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>46317</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>46274</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>46318</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>46317</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>46318</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>46317</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>45372</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>44991</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>44974</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>44623</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>46318</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45384</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>46289</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>46146</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>45576</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>45533</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>44928</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>45364</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>44701</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>45251</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>44713</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>45463</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>46013</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36075,7 +36075,7 @@
         <v>45076</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>46037</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36221,7 +36221,7 @@
         <v>44803</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45715</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>44909</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36445,7 +36445,7 @@
         <v>45996</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>45628</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45086</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>45003</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36737,7 +36737,7 @@
         <v>45632</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>44719</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36883,7 +36883,7 @@
         <v>45036</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>45365</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45096</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>45096</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>45114</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>45631</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>44783</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>44853</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45156</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37550,7 +37550,7 @@
         <v>45715</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>45485</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>45161</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>45161</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>45237</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45706</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44813</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>45224</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>45715</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>45715</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38295,7 +38295,7 @@
         <v>45719</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>45714</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         <v>45714</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38524,7 +38524,7 @@
         <v>44945</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>45008</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>45671</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38748,7 +38748,7 @@
         <v>45334</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38826,7 +38826,7 @@
         <v>45197</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>45173</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38972,7 +38972,7 @@
         <v>45238</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39045,7 +39045,7 @@
         <v>45072</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45418</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39191,7 +39191,7 @@
         <v>45068</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39264,7 +39264,7 @@
         <v>45741</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>45071</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>45111</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39488,7 +39488,7 @@
         <v>44908</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>45741</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45757</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>45222</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         <v>45097</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
         <v>45092</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39931,7 +39931,7 @@
         <v>44966</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>44953</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45391</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>45147</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45561</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40306,7 +40306,7 @@
         <v>44917</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40379,7 +40379,7 @@
         <v>45537</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>45334</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>44980</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40598,7 +40598,7 @@
         <v>45560</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40671,7 +40671,7 @@
         <v>44511</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>45468</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>45315</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45664</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44609</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41036,7 +41036,7 @@
         <v>45251</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>45161</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45344</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>45402</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>45635</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>45071</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>45523</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41547,7 +41547,7 @@
         <v>44999</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44999</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>45329</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45204</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>45706</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>45714</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>45714</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>45714</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45714</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45345</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42302,7 +42302,7 @@
         <v>44581</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42375,7 +42375,7 @@
         <v>44615</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42448,7 +42448,7 @@
         <v>45173</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45078</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42594,7 +42594,7 @@
         <v>45204</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42672,7 +42672,7 @@
         <v>45686</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>45677</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>45176</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>45239</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>45231</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45162</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45232</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>45161</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>45420</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>45223</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>45666</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45523</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43548,7 +43548,7 @@
         <v>45523</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>45195</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43694,7 +43694,7 @@
         <v>45195</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45175</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>45680</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>44685</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43991,7 +43991,7 @@
         <v>45236</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>45707</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>44908</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44215,7 +44215,7 @@
         <v>45239</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44288,7 +44288,7 @@
         <v>45315</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44361,7 +44361,7 @@
         <v>45314</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44434,7 +44434,7 @@
         <v>45314</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45463</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45328</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44653,7 +44653,7 @@
         <v>45328</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45758</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45715</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44882,7 +44882,7 @@
         <v>44746</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44955,7 +44955,7 @@
         <v>45176</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         <v>44888</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45101,7 +45101,7 @@
         <v>45264</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>44908</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45252,7 +45252,7 @@
         <v>44846</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>44846</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45398,7 +45398,7 @@
         <v>45358</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>45243</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>44630</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45209</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45695,7 +45695,7 @@
         <v>44851</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>45160</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45097</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>44848</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>45532</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46060,7 +46060,7 @@
         <v>44987</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>45391</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46206,7 +46206,7 @@
         <v>45576</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46279,7 +46279,7 @@
         <v>44739</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45349</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46425,7 +46425,7 @@
         <v>45349</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46498,7 +46498,7 @@
         <v>45349</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46571,7 +46571,7 @@
         <v>45349</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>45100</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>45100</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>45349</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>45103</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45628</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47009,7 +47009,7 @@
         <v>45349</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
         <v>45349</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>45349</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47228,7 +47228,7 @@
         <v>45042</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45349</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>45100</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45155</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47520,7 +47520,7 @@
         <v>45770</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45741</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45712</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45707</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>45804</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45916</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>45940</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>46121</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         <v>46154</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48192,7 +48192,7 @@
         <v>46166</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>46190</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>46190</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48411,7 +48411,7 @@
         <v>46153</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>46210</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
         <v>46311</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48635,7 +48635,7 @@
         <v>46315</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
